--- a/template/roster-template.xlsx
+++ b/template/roster-template.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="11">
   <si>
     <t>이름</t>
   </si>
@@ -25,7 +25,7 @@
     <t>직분</t>
   </si>
   <si>
-    <t>홍길동</t>
+    <t>유동훈</t>
   </si>
   <si>
     <t>동훈속</t>
@@ -34,19 +34,16 @@
     <t>속장</t>
   </si>
   <si>
+    <t>이영희</t>
+  </si>
+  <si>
+    <t>부속장</t>
+  </si>
+  <si>
     <t>김철수</t>
   </si>
   <si>
     <t>속원</t>
-  </si>
-  <si>
-    <t>이영희</t>
-  </si>
-  <si>
-    <t>수정속</t>
-  </si>
-  <si>
-    <t>부속장</t>
   </si>
 </sst>
 </file>
@@ -471,7 +468,7 @@
         <v>7</v>
       </c>
       <c r="B3">
-        <v>0</v>
+        <v>2001</v>
       </c>
       <c r="C3" t="s">
         <v>5</v>
@@ -485,13 +482,13 @@
         <v>9</v>
       </c>
       <c r="B4">
-        <v>2001</v>
+        <v>0</v>
       </c>
       <c r="C4" t="s">
+        <v>5</v>
+      </c>
+      <c r="D4" t="s">
         <v>10</v>
-      </c>
-      <c r="D4" t="s">
-        <v>11</v>
       </c>
     </row>
     <row r="5" spans="4:4" x14ac:dyDescent="0.25"/>
